--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_mobile_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_mobile_navigation.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
